--- a/artfynd/A 14021-2026 artfynd.xlsx
+++ b/artfynd/A 14021-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1283,6 +1283,1559 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>132815590</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Rötjärnberget syd, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>728193</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7081189</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn, Max Brändström Nyström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132815564</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Rötjärnberget syd, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>728153</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7081251</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn, Max Brändström Nyström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132815511</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Rötjärnberget syd, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>728148</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7081341</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn, Max Brändström Nyström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132815584</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Rötjärnberget syd, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>728162</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7081199</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Födosöksspår i gran</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn, Max Brändström Nyström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132815588</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91929</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Rötjärnberget syd, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>728180</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7081194</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn, Max Brändström Nyström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132815360</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Rötjärnberget syd, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>728096</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7081456</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn, Max Brändström Nyström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132815573</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Rötjärnberget syd, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>728156</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7081206</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn, Max Brändström Nyström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132815438</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91905</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Rötjärnberget syd, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>728106</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7081452</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn, Max Brändström Nyström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132815475</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92369</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Rötjärnberget syd, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>728134</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7081418</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn, Max Brändström Nyström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>132815488</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Rötjärnberget syd, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>728095</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7081400</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn, Max Brändström Nyström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132815555</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Rötjärnberget syd, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>728134</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7081337</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn, Max Brändström Nyström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>132815596</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Rötjärnberget syd, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>728164</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7081179</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn, Max Brändström Nyström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>132815604</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Rötjärnberget syd, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>728160</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7081165</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn, Max Brändström Nyström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>132815617</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Rötjärnberget syd, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>728222</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7081158</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn, Max Brändström Nyström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>132815459</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92369</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Rötjärnberget syd, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>728122</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7081442</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn, Max Brändström Nyström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14021-2026 artfynd.xlsx
+++ b/artfynd/A 14021-2026 artfynd.xlsx
@@ -2107,7 +2107,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Max Brändström Nyström</t>
+          <t>Max Brändström Nyström, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Max Brändström Nyström</t>
+          <t>Max Brändström Nyström, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2325,42 +2325,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132815555</v>
+        <v>132815596</v>
       </c>
       <c r="B17" t="n">
-        <v>57950</v>
+        <v>91872</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2368,10 +2363,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>728134</v>
+        <v>728164</v>
       </c>
       <c r="R17" t="n">
-        <v>7081337</v>
+        <v>7081179</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2412,6 +2407,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2430,37 +2426,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132815596</v>
+        <v>132815555</v>
       </c>
       <c r="B18" t="n">
-        <v>91872</v>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2468,10 +2469,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>728164</v>
+        <v>728134</v>
       </c>
       <c r="R18" t="n">
-        <v>7081179</v>
+        <v>7081337</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2512,7 +2513,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Max Brändström Nyström</t>
+          <t>Max Brändström Nyström, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 14021-2026 artfynd.xlsx
+++ b/artfynd/A 14021-2026 artfynd.xlsx
@@ -2215,46 +2215,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132815488</v>
+        <v>132815596</v>
       </c>
       <c r="B16" t="n">
-        <v>99118</v>
+        <v>91872</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2262,10 +2253,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>728095</v>
+        <v>728164</v>
       </c>
       <c r="R16" t="n">
-        <v>7081400</v>
+        <v>7081179</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2325,37 +2316,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132815596</v>
+        <v>132815555</v>
       </c>
       <c r="B17" t="n">
-        <v>91872</v>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2363,10 +2359,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>728164</v>
+        <v>728134</v>
       </c>
       <c r="R17" t="n">
-        <v>7081179</v>
+        <v>7081337</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2407,7 +2403,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2426,42 +2421,46 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132815555</v>
+        <v>132815488</v>
       </c>
       <c r="B18" t="n">
-        <v>57950</v>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2469,10 +2468,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>728134</v>
+        <v>728095</v>
       </c>
       <c r="R18" t="n">
-        <v>7081337</v>
+        <v>7081400</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2513,6 +2512,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 14021-2026 artfynd.xlsx
+++ b/artfynd/A 14021-2026 artfynd.xlsx
@@ -1288,7 +1288,7 @@
         <v>132815590</v>
       </c>
       <c r="B7" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>132815564</v>
       </c>
       <c r="B8" t="n">
-        <v>57141</v>
+        <v>57142</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>132815511</v>
       </c>
       <c r="B9" t="n">
-        <v>58114</v>
+        <v>58115</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>132815584</v>
       </c>
       <c r="B10" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1714,10 +1714,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132815588</v>
+        <v>132815360</v>
       </c>
       <c r="B11" t="n">
-        <v>91929</v>
+        <v>91910</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1725,19 +1725,23 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -1748,10 +1752,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>728180</v>
+        <v>728096</v>
       </c>
       <c r="R11" t="n">
-        <v>7081194</v>
+        <v>7081456</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1811,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132815360</v>
+        <v>132815588</v>
       </c>
       <c r="B12" t="n">
-        <v>91909</v>
+        <v>91930</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1822,23 +1826,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -1849,10 +1849,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>728096</v>
+        <v>728180</v>
       </c>
       <c r="R12" t="n">
-        <v>7081456</v>
+        <v>7081194</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1915,7 +1915,7 @@
         <v>132815573</v>
       </c>
       <c r="B13" t="n">
-        <v>92632</v>
+        <v>92633</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>132815438</v>
       </c>
       <c r="B14" t="n">
-        <v>91905</v>
+        <v>91906</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Max Brändström Nyström, Isac Enetjärn</t>
+          <t>Isac Enetjärn, Max Brändström Nyström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2117,7 +2117,7 @@
         <v>132815475</v>
       </c>
       <c r="B15" t="n">
-        <v>92369</v>
+        <v>92370</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2208,44 +2208,49 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Max Brändström Nyström, Isac Enetjärn</t>
+          <t>Isac Enetjärn, Max Brändström Nyström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132815596</v>
+        <v>132815555</v>
       </c>
       <c r="B16" t="n">
-        <v>91872</v>
+        <v>57951</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2253,10 +2258,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>728164</v>
+        <v>728134</v>
       </c>
       <c r="R16" t="n">
-        <v>7081179</v>
+        <v>7081337</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2297,7 +2302,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2316,42 +2320,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132815555</v>
+        <v>132815596</v>
       </c>
       <c r="B17" t="n">
-        <v>57950</v>
+        <v>91873</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2359,10 +2358,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>728134</v>
+        <v>728164</v>
       </c>
       <c r="R17" t="n">
-        <v>7081337</v>
+        <v>7081179</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2403,6 +2402,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2424,7 +2424,7 @@
         <v>132815488</v>
       </c>
       <c r="B18" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>132815604</v>
       </c>
       <c r="B19" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2636,32 +2636,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132815617</v>
+        <v>132815459</v>
       </c>
       <c r="B20" t="n">
-        <v>92632</v>
+        <v>92370</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3298</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2674,10 +2674,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>728222</v>
+        <v>728122</v>
       </c>
       <c r="R20" t="n">
-        <v>7081158</v>
+        <v>7081442</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2737,32 +2737,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132815459</v>
+        <v>132815617</v>
       </c>
       <c r="B21" t="n">
-        <v>92369</v>
+        <v>92633</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>3298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>728122</v>
+        <v>728222</v>
       </c>
       <c r="R21" t="n">
-        <v>7081442</v>
+        <v>7081158</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Max Brändström Nyström, Isac Enetjärn</t>
+          <t>Isac Enetjärn, Max Brändström Nyström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 14021-2026 artfynd.xlsx
+++ b/artfynd/A 14021-2026 artfynd.xlsx
@@ -1288,7 +1288,7 @@
         <v>132815590</v>
       </c>
       <c r="B7" t="n">
-        <v>91910</v>
+        <v>91912</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>132815360</v>
       </c>
       <c r="B11" t="n">
-        <v>91910</v>
+        <v>91912</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>132815588</v>
       </c>
       <c r="B12" t="n">
-        <v>91930</v>
+        <v>91932</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>132815573</v>
       </c>
       <c r="B13" t="n">
-        <v>92633</v>
+        <v>92635</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>132815438</v>
       </c>
       <c r="B14" t="n">
-        <v>91906</v>
+        <v>91908</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>132815475</v>
       </c>
       <c r="B15" t="n">
-        <v>92370</v>
+        <v>92372</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2215,42 +2215,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132815555</v>
+        <v>132815596</v>
       </c>
       <c r="B16" t="n">
-        <v>57951</v>
+        <v>91875</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2258,10 +2253,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>728134</v>
+        <v>728164</v>
       </c>
       <c r="R16" t="n">
-        <v>7081337</v>
+        <v>7081179</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2302,6 +2297,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2320,37 +2316,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132815596</v>
+        <v>132815555</v>
       </c>
       <c r="B17" t="n">
-        <v>91873</v>
+        <v>57951</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2358,10 +2359,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>728164</v>
+        <v>728134</v>
       </c>
       <c r="R17" t="n">
-        <v>7081179</v>
+        <v>7081337</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2402,7 +2403,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2424,7 +2424,7 @@
         <v>132815488</v>
       </c>
       <c r="B18" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2636,32 +2636,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132815459</v>
+        <v>132815617</v>
       </c>
       <c r="B20" t="n">
-        <v>92370</v>
+        <v>92635</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>3298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2674,10 +2674,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>728122</v>
+        <v>728222</v>
       </c>
       <c r="R20" t="n">
-        <v>7081442</v>
+        <v>7081158</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2737,32 +2737,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132815617</v>
+        <v>132815459</v>
       </c>
       <c r="B21" t="n">
-        <v>92633</v>
+        <v>92372</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3298</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>728222</v>
+        <v>728122</v>
       </c>
       <c r="R21" t="n">
-        <v>7081158</v>
+        <v>7081442</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 14021-2026 artfynd.xlsx
+++ b/artfynd/A 14021-2026 artfynd.xlsx
@@ -1288,7 +1288,7 @@
         <v>132815590</v>
       </c>
       <c r="B7" t="n">
-        <v>91912</v>
+        <v>91913</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1714,10 +1714,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132815360</v>
+        <v>132815588</v>
       </c>
       <c r="B11" t="n">
-        <v>91912</v>
+        <v>91933</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1725,23 +1725,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -1752,10 +1748,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>728096</v>
+        <v>728180</v>
       </c>
       <c r="R11" t="n">
-        <v>7081456</v>
+        <v>7081194</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1815,10 +1811,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132815588</v>
+        <v>132815360</v>
       </c>
       <c r="B12" t="n">
-        <v>91932</v>
+        <v>91913</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1826,19 +1822,23 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -1849,10 +1849,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>728180</v>
+        <v>728096</v>
       </c>
       <c r="R12" t="n">
-        <v>7081194</v>
+        <v>7081456</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1915,7 +1915,7 @@
         <v>132815573</v>
       </c>
       <c r="B13" t="n">
-        <v>92635</v>
+        <v>92636</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>132815438</v>
       </c>
       <c r="B14" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Max Brändström Nyström</t>
+          <t>Max Brändström Nyström, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2117,7 +2117,7 @@
         <v>132815475</v>
       </c>
       <c r="B15" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Max Brändström Nyström</t>
+          <t>Max Brändström Nyström, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2218,7 +2218,7 @@
         <v>132815596</v>
       </c>
       <c r="B16" t="n">
-        <v>91875</v>
+        <v>91876</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>132815488</v>
       </c>
       <c r="B18" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2636,32 +2636,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132815617</v>
+        <v>132815459</v>
       </c>
       <c r="B20" t="n">
-        <v>92635</v>
+        <v>92373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3298</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2674,10 +2674,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>728222</v>
+        <v>728122</v>
       </c>
       <c r="R20" t="n">
-        <v>7081158</v>
+        <v>7081442</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2730,39 +2730,39 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Max Brändström Nyström</t>
+          <t>Max Brändström Nyström, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132815459</v>
+        <v>132815617</v>
       </c>
       <c r="B21" t="n">
-        <v>92372</v>
+        <v>92636</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>3298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>728122</v>
+        <v>728222</v>
       </c>
       <c r="R21" t="n">
-        <v>7081442</v>
+        <v>7081158</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 14021-2026 artfynd.xlsx
+++ b/artfynd/A 14021-2026 artfynd.xlsx
@@ -2107,7 +2107,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Max Brändström Nyström, Isac Enetjärn</t>
+          <t>Isac Enetjärn, Max Brändström Nyström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Max Brändström Nyström, Isac Enetjärn</t>
+          <t>Isac Enetjärn, Max Brändström Nyström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Max Brändström Nyström, Isac Enetjärn</t>
+          <t>Isac Enetjärn, Max Brändström Nyström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 14021-2026 artfynd.xlsx
+++ b/artfynd/A 14021-2026 artfynd.xlsx
@@ -2215,37 +2215,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132815596</v>
+        <v>132815555</v>
       </c>
       <c r="B16" t="n">
-        <v>91881</v>
+        <v>57955</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2253,10 +2258,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>728164</v>
+        <v>728134</v>
       </c>
       <c r="R16" t="n">
-        <v>7081179</v>
+        <v>7081337</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2297,7 +2302,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2316,42 +2320,46 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132815555</v>
+        <v>132815488</v>
       </c>
       <c r="B17" t="n">
-        <v>57955</v>
+        <v>99130</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2359,10 +2367,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>728134</v>
+        <v>728095</v>
       </c>
       <c r="R17" t="n">
-        <v>7081337</v>
+        <v>7081400</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2403,6 +2411,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2421,46 +2430,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132815488</v>
+        <v>132815596</v>
       </c>
       <c r="B18" t="n">
-        <v>99130</v>
+        <v>91881</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2468,10 +2468,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>728095</v>
+        <v>728164</v>
       </c>
       <c r="R18" t="n">
-        <v>7081400</v>
+        <v>7081179</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 14021-2026 artfynd.xlsx
+++ b/artfynd/A 14021-2026 artfynd.xlsx
@@ -2215,42 +2215,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132815555</v>
+        <v>132815596</v>
       </c>
       <c r="B16" t="n">
-        <v>57955</v>
+        <v>91881</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2258,10 +2253,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>728134</v>
+        <v>728164</v>
       </c>
       <c r="R16" t="n">
-        <v>7081337</v>
+        <v>7081179</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2302,6 +2297,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2320,46 +2316,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132815488</v>
+        <v>132815555</v>
       </c>
       <c r="B17" t="n">
-        <v>99130</v>
+        <v>57955</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2367,10 +2359,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>728095</v>
+        <v>728134</v>
       </c>
       <c r="R17" t="n">
-        <v>7081400</v>
+        <v>7081337</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2411,7 +2403,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2430,37 +2421,46 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132815596</v>
+        <v>132815488</v>
       </c>
       <c r="B18" t="n">
-        <v>91881</v>
+        <v>99130</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2468,10 +2468,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>728164</v>
+        <v>728095</v>
       </c>
       <c r="R18" t="n">
-        <v>7081179</v>
+        <v>7081400</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 14021-2026 artfynd.xlsx
+++ b/artfynd/A 14021-2026 artfynd.xlsx
@@ -1379,7 +1379,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Max Brändström Nyström</t>
+          <t>Max Brändström Nyström, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Max Brändström Nyström</t>
+          <t>Max Brändström Nyström, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Max Brändström Nyström</t>
+          <t>Max Brändström Nyström, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Max Brändström Nyström</t>
+          <t>Max Brändström Nyström, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Max Brändström Nyström</t>
+          <t>Max Brändström Nyström, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Max Brändström Nyström</t>
+          <t>Max Brändström Nyström, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Max Brändström Nyström</t>
+          <t>Max Brändström Nyström, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Max Brändström Nyström</t>
+          <t>Max Brändström Nyström, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Max Brändström Nyström</t>
+          <t>Max Brändström Nyström, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 14021-2026 artfynd.xlsx
+++ b/artfynd/A 14021-2026 artfynd.xlsx
@@ -1379,7 +1379,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Max Brändström Nyström, Isac Enetjärn</t>
+          <t>Isac Enetjärn, Max Brändström Nyström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Max Brändström Nyström, Isac Enetjärn</t>
+          <t>Isac Enetjärn, Max Brändström Nyström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Max Brändström Nyström, Isac Enetjärn</t>
+          <t>Isac Enetjärn, Max Brändström Nyström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1707,17 +1707,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Max Brändström Nyström, Isac Enetjärn</t>
+          <t>Isac Enetjärn, Max Brändström Nyström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132815360</v>
+        <v>132815588</v>
       </c>
       <c r="B11" t="n">
-        <v>91918</v>
+        <v>91938</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1725,23 +1725,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -1752,10 +1748,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>728096</v>
+        <v>728180</v>
       </c>
       <c r="R11" t="n">
-        <v>7081456</v>
+        <v>7081194</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1815,10 +1811,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132815588</v>
+        <v>132815360</v>
       </c>
       <c r="B12" t="n">
-        <v>91938</v>
+        <v>91918</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1826,19 +1822,23 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -1849,10 +1849,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>728180</v>
+        <v>728096</v>
       </c>
       <c r="R12" t="n">
-        <v>7081194</v>
+        <v>7081456</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Max Brändström Nyström, Isac Enetjärn</t>
+          <t>Isac Enetjärn, Max Brändström Nyström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Max Brändström Nyström, Isac Enetjärn</t>
+          <t>Isac Enetjärn, Max Brändström Nyström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Max Brändström Nyström, Isac Enetjärn</t>
+          <t>Isac Enetjärn, Max Brändström Nyström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Max Brändström Nyström, Isac Enetjärn</t>
+          <t>Isac Enetjärn, Max Brändström Nyström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2629,39 +2629,39 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Max Brändström Nyström, Isac Enetjärn</t>
+          <t>Isac Enetjärn, Max Brändström Nyström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132815459</v>
+        <v>132815617</v>
       </c>
       <c r="B20" t="n">
-        <v>92378</v>
+        <v>92641</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>3298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2674,10 +2674,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>728122</v>
+        <v>728222</v>
       </c>
       <c r="R20" t="n">
-        <v>7081442</v>
+        <v>7081158</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2737,32 +2737,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132815617</v>
+        <v>132815459</v>
       </c>
       <c r="B21" t="n">
-        <v>92641</v>
+        <v>92378</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3298</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>728222</v>
+        <v>728122</v>
       </c>
       <c r="R21" t="n">
-        <v>7081158</v>
+        <v>7081442</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 14021-2026 artfynd.xlsx
+++ b/artfynd/A 14021-2026 artfynd.xlsx
@@ -2215,37 +2215,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132815596</v>
+        <v>132815555</v>
       </c>
       <c r="B16" t="n">
-        <v>91881</v>
+        <v>57955</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2253,10 +2258,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>728164</v>
+        <v>728134</v>
       </c>
       <c r="R16" t="n">
-        <v>7081179</v>
+        <v>7081337</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2297,7 +2302,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2316,42 +2320,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132815555</v>
+        <v>132815596</v>
       </c>
       <c r="B17" t="n">
-        <v>57955</v>
+        <v>91881</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2359,10 +2358,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>728134</v>
+        <v>728164</v>
       </c>
       <c r="R17" t="n">
-        <v>7081337</v>
+        <v>7081179</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2403,6 +2402,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 14021-2026 artfynd.xlsx
+++ b/artfynd/A 14021-2026 artfynd.xlsx
@@ -2215,42 +2215,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132815555</v>
+        <v>132815596</v>
       </c>
       <c r="B16" t="n">
-        <v>57955</v>
+        <v>91881</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2258,10 +2253,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>728134</v>
+        <v>728164</v>
       </c>
       <c r="R16" t="n">
-        <v>7081337</v>
+        <v>7081179</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2302,6 +2297,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2320,37 +2316,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132815596</v>
+        <v>132815555</v>
       </c>
       <c r="B17" t="n">
-        <v>91881</v>
+        <v>57955</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2358,10 +2359,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>728164</v>
+        <v>728134</v>
       </c>
       <c r="R17" t="n">
-        <v>7081179</v>
+        <v>7081337</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2402,7 +2403,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 14021-2026 artfynd.xlsx
+++ b/artfynd/A 14021-2026 artfynd.xlsx
@@ -2316,42 +2316,46 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132815555</v>
+        <v>132815488</v>
       </c>
       <c r="B17" t="n">
-        <v>57955</v>
+        <v>99130</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2359,10 +2363,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>728134</v>
+        <v>728095</v>
       </c>
       <c r="R17" t="n">
-        <v>7081337</v>
+        <v>7081400</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2403,6 +2407,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2421,46 +2426,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132815488</v>
+        <v>132815555</v>
       </c>
       <c r="B18" t="n">
-        <v>99130</v>
+        <v>57955</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2468,10 +2469,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>728095</v>
+        <v>728134</v>
       </c>
       <c r="R18" t="n">
-        <v>7081400</v>
+        <v>7081337</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2512,7 +2513,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
